--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260709.xlsx
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>243,047,501</t>
+          <t>1,237,440</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2,037,320</t>
+          <t>243,047,501</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,237,440</t>
+          <t>2,037,320</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
